--- a/www/download/COUNTRY.BGR.rpO1.xlsx
+++ b/www/download/COUNTRY.BGR.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.0671456399048756</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.129019769453539</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.55465380102638</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1.75697525069061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.83398739185676</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2.11747769546194</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.18321545619096</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.0705219732609</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1.72965500230581</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.5735146527652</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.57168460694959</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1.55789934671618</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.42700168561391</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.33054449933994</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.4031148969898</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.519</t>
+          <t>1.48513414295212</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.614</t>
+          <t>1.41847473817385</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.33379653085755</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>1.35410320823055</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.312</t>
+          <t>1.46679813804646</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>1.44498745103157</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.215</t>
+          <t>1.38224674708078</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.222</t>
+          <t>1.42494294037268</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.317</t>
+          <t>2.28129051500125</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.404</t>
+          <t>1.5629786580783</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>1.56699225312771</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.612</t>
+          <t>1.55253174322975</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>1.54207126990707</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.54418034145495</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>1.50131098122394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>3.08653954945979</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2.97263217731629</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.86837956518391</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.528</t>
+          <t>2.92210583318951</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.09154111630277</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>3.01358581272916</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.272</t>
+          <t>2.92012508507781</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>2.99769944417919</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>4.70960685968039</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.432</t>
+          <t>3.12478583550846</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>3.19260569922156</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.631</t>
+          <t>3.06970637331579</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.02681604586821</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.817</t>
+          <t>3.04864200972948</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>2.94187960178339</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6025.009</t>
+          <t>4.10516369415221</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6178.773</t>
+          <t>3.94941141404713</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5980.411</t>
+          <t>3.7806581438858</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5727.669</t>
+          <t>3.74025683563675</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5532.414</t>
+          <t>3.94485942418349</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5313.109</t>
+          <t>3.87198060405639</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5310.295</t>
+          <t>3.75153697992074</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5320.554</t>
+          <t>3.84295627282676</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5442.215</t>
+          <t>3.28840705937563</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5662.196</t>
+          <t>3.94260577852254</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5797.413</t>
+          <t>3.99009828177986</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5998.505</t>
+          <t>3.90471309157344</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6165.971</t>
+          <t>3.75613605986404</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6241.306</t>
+          <t>3.65271607930556</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6207.343</t>
+          <t>3.59024377895773</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4763.822</t>
+          <t>869635009862.295</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4804.766</t>
+          <t>812017835239.891</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4583.11</t>
+          <t>670844701141.402</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4317.376</t>
+          <t>809196697426.37</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4123.538</t>
+          <t>833794958988.777</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3934.009</t>
+          <t>877348451161.209</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3898.358</t>
+          <t>981991342681.094</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3902.291</t>
+          <t>1037024426015.48</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4004.834</t>
+          <t>1271062531427.77</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4138.132</t>
+          <t>1306117231157.62</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4244.756</t>
+          <t>1307972144663.32</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4411.226</t>
+          <t>1333571109351.67</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4582.662</t>
+          <t>1309764885938.7</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4717.103</t>
+          <t>1199800241778.63</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4560.187</t>
+          <t>1129111963470.04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>98494086679.7543</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>80599367066.3167</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>62559871405.2066</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>90724219499.1315</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>93723105843.5039</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>96870805748.8326</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>112405233483.793</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>121291065140.732</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>150145781526.859</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>147278228514.69</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>143932434336.293</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>137802252279.271</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>135994117955.214</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>131778397721.845</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>128961087513.335</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>1090969314.44526</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>909243222.286337</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>950895435.841977</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>1097156131.77722</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1124985073.86102</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>1180109162.37682</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>1265557503.47193</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>1206328506.87393</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>1098222642.73343</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>883876484.44477</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>775045801.965129</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>670690225.067299</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>504028532.435667</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>393846095.547761</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>387263581.494448</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>17704.0231443909</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>17117.6709391217</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>13617.0343120138</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>16636.3668298385</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>16088.9469474049</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>14501.4247358027</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>15206.6252702142</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>16959.9159787165</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>21470.1335647291</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>25663.396092615</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>27727.8085055009</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>30462.7976804498</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>39977.9108508523</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>50062.6600453904</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>51427.9447956712</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>39095.9050432467</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>41003.4374120515</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>33163.1783934476</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>36302.7431201266</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>34868.0565243439</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>32350.2250857051</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>34238.5039092819</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>37803.4315944699</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>48685.0519566717</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>60129.1352067366</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>67403.029071526</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>79716.1016114284</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>104410.245817158</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>127428.195104201</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>124850.820357061</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>3447.72564488812</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>4056.45139437598</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3529.51632179635</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>3363.56304269644</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>3536.89036522245</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>3192.59913736407</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>3620.46079664702</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>4158.10523720059</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>5161.27485912345</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>5890.67711845049</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>6688.3511466785</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>8068.78907233715</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>9931.60253167939</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>12849.9641821979</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>11756.8761003702</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.0671456399048756</t>
+          <t>36301.685999686</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.129019769453539</t>
+          <t>29488.8484586309</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.55465380102638</t>
+          <t>24153.280135406</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.75697525069061</t>
+          <t>35883.9322956185</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.83398739185676</t>
+          <t>39212.6497486428</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.11747769546194</t>
+          <t>41655.904428653</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.18321545619096</t>
+          <t>49467.6026421655</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.0705219732609</t>
+          <t>53183.8398407136</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.72965500230581</t>
+          <t>63481.2199927527</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.5735146527652</t>
+          <t>60558.482119527</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.57168460694959</t>
+          <t>57054.9151053605</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.55789934671618</t>
+          <t>52376.3786694304</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.42700168561391</t>
+          <t>49627.4561015998</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.33054449933994</t>
+          <t>46776.372895728</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.4031148969898</t>
+          <t>47351.2346294604</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-31682682386.1718</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-13474166215.1789</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-10942666435.202</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-25895885407.0346</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-16596635789.2155</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>7539060245.25007</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>14585382678.551</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>16397946210.0968</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>28515778905.8306</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>41721851510.5751</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>38428198235.3579</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>63037610246.4093</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>54470854401.1692</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>28908850302.8509</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>10753992944.2077</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-37610444509.8871</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-23900621399.1467</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-16529893780.4044</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-29042495505.7242</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-17855029865.4621</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2064048408.07256</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-14362988043.3086</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-18626965718.3515</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-9064479515.87563</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-169794881.376569</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>7242053415.71731</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14537652216.7776</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>18958477854.4255</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>6544507280.93882</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-15859119831.5108</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>5927762123.71528</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>10426455183.9679</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>5587227345.20241</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>3146610098.68965</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1258394076.24661</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>5475011837.17751</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>28948370721.8596</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>35024911928.4483</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>37580258421.7063</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>41891646391.9517</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>31186144819.6406</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>48499958029.6317</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>35512376546.7437</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>22364343021.912</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>26613112775.7185</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>162721.495752318</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>128261.24111245</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>102344.172210454</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>151231.692311125</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>170462.479416507</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>177535.63731504</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>205153.982132036</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>223698.247967064</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>274495.963258301</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>254268.153496666</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>241180.999429302</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>216972.325238135</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>201015.971452661</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>184755.212075478</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>183089.774542076</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>152995.205747211</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>126996.180620985</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>106392.718378924</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>157779.091799513</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>173496.929102028</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>186568.336706917</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>218425.493283781</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>234869.598759402</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>285207.745556582</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>281259.612797246</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>271098.158226435</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>252255.001407973</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>240456.442998689</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>231479.819092175</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>235115.827927373</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>148.51</t>
+          <t>5721.26684707971</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>141.85</t>
+          <t>7358.52060140411</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>133.38</t>
+          <t>6196.35018071592</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>135.41</t>
+          <t>5779.99963217886</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>146.68</t>
+          <t>6949.75614597142</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>6339.86696377089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>6298.97003500614</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>142.49</t>
+          <t>7064.93906070471</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>228.13</t>
+          <t>9391.07357302661</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>156.3</t>
+          <t>12285.3479543285</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>10701.9758549452</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>155.25</t>
+          <t>15598.6154976521</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>154.21</t>
+          <t>23672.799380887</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>154.42</t>
+          <t>28533.0144010217</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>150.13</t>
+          <t>21725.163896309</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>308.65</t>
+          <t>214077163769.986</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>297.26</t>
+          <t>231211724793.07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>286.84</t>
+          <t>204617509622.462</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>292.21</t>
+          <t>223614673477.298</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>309.15</t>
+          <t>267660375072.014</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>301.36</t>
+          <t>254569275899.342</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>292.01</t>
+          <t>260806953073.223</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>299.77</t>
+          <t>285644891095.892</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>470.96</t>
+          <t>354355160873.934</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>312.48</t>
+          <t>371850644317.421</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>319.26</t>
+          <t>287084700591.429</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>306.97</t>
+          <t>344256284275.841</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>302.68</t>
+          <t>395370850535.803</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>304.86</t>
+          <t>382613789948.737</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>294.19</t>
+          <t>297243661217.226</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>410.52</t>
+          <t>5490.23842158157</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>394.94</t>
+          <t>6176.15579939194</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>378.07</t>
+          <t>5302.77511120537</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>374.03</t>
+          <t>5314.21712516818</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>394.49</t>
+          <t>7204.36396197689</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>387.2</t>
+          <t>6601.36411143601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>375.15</t>
+          <t>7146.01509412255</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>384.3</t>
+          <t>7993.22441665403</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>328.84</t>
+          <t>10928.7375165054</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>394.26</t>
+          <t>14474.4025210414</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>399.01</t>
+          <t>14190.5286717511</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>390.47</t>
+          <t>20576.4268715346</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>375.61</t>
+          <t>30675.4328324775</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>365.27</t>
+          <t>37860.2439430891</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>359.02</t>
+          <t>24912.5895408874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>538354.752</t>
+          <t>173962649873.025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>458933.409</t>
+          <t>179257739077.883</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>372427.2</t>
+          <t>163886947545.976</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>547887.366</t>
+          <t>180251336057.457</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>574692.567</t>
+          <t>261344089035.118</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>604350.813</t>
+          <t>274007356248.024</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>702194.276</t>
+          <t>316840383818.523</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>756796.821</t>
+          <t>345834914776.911</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>946148.175</t>
+          <t>451199452820.657</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>957267.092</t>
+          <t>493362455987.094</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>947542.283</t>
+          <t>438555304547.75</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>911145.065</t>
+          <t>544810966231.664</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>896084.98</t>
+          <t>592279443024.24</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>870273.039</t>
+          <t>551753610506.145</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>879275.644</t>
+          <t>355151850051.988</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>441497.541</t>
+          <t>231.028425498138</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>350565.566</t>
+          <t>1182.36480201217</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>265083.592</t>
+          <t>893.575069510543</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>382354.34</t>
+          <t>465.782507010675</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>407426.509</t>
+          <t>-254.607816005468</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>412859.125</t>
+          <t>-261.497147665119</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>466171.394</t>
+          <t>-847.045059116402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>510166.224</t>
+          <t>-928.285355949323</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>649237.852</t>
+          <t>-1537.66394347881</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>618380.149</t>
+          <t>-2189.05456671294</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>608427.307</t>
+          <t>-3488.55281680589</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>570854.188</t>
+          <t>-4977.81137388255</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>550844.067</t>
+          <t>-7002.63345159048</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>520492.383</t>
+          <t>-9327.22954206735</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>498645.001</t>
+          <t>-3187.42564457845</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>869635.01</t>
+          <t>40114513896.961</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>812017.835</t>
+          <t>51953985715.1864</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>670844.701</t>
+          <t>40730562076.4864</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>809196.697</t>
+          <t>43363337419.8406</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>833794.959</t>
+          <t>6316286036.89598</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>877348.451</t>
+          <t>-19438080348.6819</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>981991.343</t>
+          <t>-56033430745.2995</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1037024.426</t>
+          <t>-60190023681.019</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1271062.531</t>
+          <t>-96844291946.7232</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1306117.231</t>
+          <t>-121511811669.673</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1307972.145</t>
+          <t>-151470603956.321</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1333571.109</t>
+          <t>-200554681955.823</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1309764.886</t>
+          <t>-196908592488.437</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1199800.242</t>
+          <t>-169139820557.408</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1129111.963</t>
+          <t>-57908188834.7621</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>7012.30761</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>6877.74777</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>6270.65211</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>6914.69346</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>6670.10395</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>6416.64399</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>6743.30415</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>7429.86574</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>9358.55309</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>11103.62409</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>11861.38017</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>13600.24546</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>17476.37378</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>20824.95179</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>19526.1047</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>393801.814</t>
+          <t>0.0380771013870919</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>338992.411</t>
+          <t>0.036029677244025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>275453.553</t>
+          <t>0.0264435587272494</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>370828.536</t>
+          <t>0.0312512803716646</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>384732.738</t>
+          <t>0.0350731110414279</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>393283.277</t>
+          <t>0.0502406308041642</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>436139.803</t>
+          <t>0.0486879810313237</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>465244.725</t>
+          <t>0.050289189476238</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>560539.246</t>
+          <t>0.0481763610183856</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>557456.942</t>
+          <t>0.0528344823709086</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>538064.856</t>
+          <t>0.0477227532527287</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>509612.313</t>
+          <t>0.0467491783259182</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>501499.287</t>
+          <t>0.0501451606622436</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>471365.003</t>
+          <t>0.036373665675204</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>465098.327</t>
+          <t>0.0299956595016292</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>5489.46630861788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>5006.89951687757</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>3785.66597417408</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>4945.03266376072</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>4798.34269918028</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4380.49479616497</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4758.44007447194</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>5335.1763633511</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>6958.43965857143</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>8259.53538536535</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>9075.80306826029</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>10152.1320669268</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>13383.0860932627</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>17345.3482740352</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>17471.3095980248</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>98494.087</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>80599.367</t>
+          <t>6217.29677098901</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62559.871</t>
+          <t>4798.85981629446</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>90724.219</t>
+          <t>6259.01049800769</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>93723.106</t>
+          <t>6036.95211304725</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>96870.806</t>
+          <t>5484.63915254219</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>112405.233</t>
+          <t>5928.87398593274</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>121291.065</t>
+          <t>6628.1048903259</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>150145.782</t>
+          <t>8671.86455135768</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>147278.229</t>
+          <t>10430.9043908861</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>143932.434</t>
+          <t>11518.9534811051</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>137802.252</t>
+          <t>12840.3745381041</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>135994.118</t>
+          <t>16776.530543474</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>131778.398</t>
+          <t>21718.3063310489</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>128961.088</t>
+          <t>22406.6496559926</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>59355.9918630032</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>69181.360625382</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>57565.0534638733</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>57282.9470666745</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>56099.0221085957</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>49644.40832393</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>51815.9310363921</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>56629.2617187464</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>69005.7104614056</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>81828.1596914803</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>94664.9996971436</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>108329.971368739</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>134829.532811473</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>171064.196342325</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>169178.186375985</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1090.969</t>
+          <t>6607.49241501291</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>909.243</t>
+          <t>5584.61395596881</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>950.895</t>
+          <t>5355.12594675398</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1097.156</t>
+          <t>6252.61889475759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1124.985</t>
+          <t>6075.67002837942</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1180.109</t>
+          <t>5928.32673597345</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1265.558</t>
+          <t>6194.74997422339</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1206.329</t>
+          <t>6389.92025212374</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1098.223</t>
+          <t>6725.03702834154</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>883.876</t>
+          <t>7048.28016969507</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>775.046</t>
+          <t>7484.59364170855</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>670.69</t>
+          <t>7785.80118759571</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>504.029</t>
+          <t>8447.78820222002</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>393.846</t>
+          <t>9793.18926755484</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>387.264</t>
+          <t>11135.2774240175</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5489.46630861788</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4474.00496783007</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4351.7116477922</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4818.72925768776</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4544.72734306569</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4475.68133504424</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4735.73989088866</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4844.02819302775</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5039.88997323793</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5141.88656144408</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5458.5149271311</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5602.33644205346</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6254.31714764814</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7238.47960290336</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7446.98105217487</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5707.82976498709</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6549.03348901099</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5051.74119370554</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5153.72848199231</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>5504.45759695275</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5686.76552745781</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6143.27386406726</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>7005.9449096741</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8485.71887864231</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10214.0255791139</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11206.0255688949</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>13133.1262218959</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16692.651116526</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>19072.1960689511</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>16831.4873740074</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>441497541117.697</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>350565566075.13</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>265083591821.253</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>382354339971.123</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>407426509126.75</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>412859124576.126</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>466171393598.625</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>510166224313.686</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>649237852298.534</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>618380149303.893</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>608427307260.299</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>570854187701.533</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>550844066571.727</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>520492383459.036</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>498645000965.344</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>538354752307.838</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>458933409425.92</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>372427200436.653</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>547887365850.213</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>574692566782.437</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>604350813094.718</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>702194275808.698</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>756796821122.546</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>946148175109.407</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>957267092155.428</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>947542282633.035</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>911145065085.598</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>896084980478.915</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>870273038877.905</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>879275643504.779</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>393801814403.427</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>338992410822.832</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>275453552886.233</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>370828536326.65</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>384732738138.652</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>393283276944.161</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>436139803488.833</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>465244724917.302</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>560539246074.219</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>557456942151.931</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>538064856391.962</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>509612312637.838</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>501499287122.926</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>471365003462.727</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>465098327423.085</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3518768.77238457</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3613757.57272251</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3500495.20410063</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3472496.63818831</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3312407.71670649</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3239300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3214800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3222200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3317400</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3403500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3495200</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3612000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3726600</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3759606.5276488</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3739755.21450808</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2713209.70272858</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2733215.13993289</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2590119.06683022</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2528268.60645396</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2390124.26970069</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2325500</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2272300</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2280600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2365200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2432000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2522700</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2631000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2740300</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2817200</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2723500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6025008671.9305</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6178772891.40574</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5980411261.78583</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5727669207.89169</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5532413588.31211</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5313109000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5310295000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5320554000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5442215000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5662196000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5797413000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5998505000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6165971000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6241305983.29216</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6207342931.12282</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4763821895.65152</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4804766257.4269</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4583109986.79267</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4317376468.78796</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4123537525.08647</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3934009000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3898358000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3902291000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4004834000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4138132000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4244756000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4411226000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4582661529.17968</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4717103117.13106</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4560187201.07867</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>28401.43623</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>30820.60983</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24225.98663</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25554.54324</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>25628.093</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>25699.58624</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>27780.08002</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>31008.8956</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>40492.17933</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>51515.12221</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>59695.11906</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>71335.35282</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>92537.04128</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>110695.73757</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>106237.58348</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>12315.32218</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>12766.33026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9850.60101</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>11412.73898</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>11541.40971</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>11171.40468</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12072.14785</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>13634.0498</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>17157.58343</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20644.92997</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>22724.97905</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>25973.50076</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>33469.18166</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>40790.5024</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>39238.13703</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3985.49606034859</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3959.94442489811</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3912.92233580997</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3897.84900789496</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3908.98421005755</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3942.36819554376</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4007.15957625372</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4082.12838080333</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4178.98220818302</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4301.6328803054</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4499.12178577914</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4729.83595275513</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4992.82783053041</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>5336.88681506164</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5500.80095714951</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
